--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H3">
         <v>426</v>
